--- a/salidas/empresas/TGT.xlsx
+++ b/salidas/empresas/TGT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>32.70330810546875</v>
+        <v>32.70330047607422</v>
       </c>
       <c r="C2" t="n">
         <v>54.75</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.55296325683594</v>
+        <v>32.55297470092773</v>
       </c>
       <c r="C3" t="n">
         <v>54.40000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.12277412414551</v>
+        <v>31.12278938293457</v>
       </c>
       <c r="C4" t="n">
         <v>52.0099983215332</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.7750415802002</v>
+        <v>31.77504539489746</v>
       </c>
       <c r="C5" t="n">
         <v>53.09999847412109</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.33319282531738</v>
+        <v>29.33319091796875</v>
       </c>
       <c r="C6" t="n">
         <v>48.91999816894531</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>29.30322074890137</v>
+        <v>29.30321311950684</v>
       </c>
       <c r="C7" t="n">
         <v>48.86999893188477</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53435897827148</v>
+        <v>27.53435516357422</v>
       </c>
       <c r="C8" t="n">
         <v>45.91999816894531</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.08710479736328</v>
+        <v>29.08711051940918</v>
       </c>
       <c r="C9" t="n">
         <v>48.38999938964844</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>33.21064376831055</v>
+        <v>33.21061706542969</v>
       </c>
       <c r="C10" t="n">
         <v>55.25</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>34.98980712890625</v>
+        <v>34.98979568481445</v>
       </c>
       <c r="C12" t="n">
         <v>58.09000015258789</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>34.36336135864258</v>
+        <v>34.36337280273438</v>
       </c>
       <c r="C13" t="n">
         <v>57.04999923706055</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>37.13321304321289</v>
+        <v>37.13320159912109</v>
       </c>
       <c r="C15" t="n">
         <v>61.52999877929688</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>35.76327133178711</v>
+        <v>35.76327514648438</v>
       </c>
       <c r="C16" t="n">
         <v>59.2599983215332</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>35.82964324951172</v>
+        <v>35.82966613769531</v>
       </c>
       <c r="C17" t="n">
         <v>59.36999893188477</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>37.75508880615234</v>
+        <v>37.75508117675781</v>
       </c>
       <c r="C18" t="n">
         <v>62.43000030517578</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>38.46265029907227</v>
+        <v>38.4626579284668</v>
       </c>
       <c r="C19" t="n">
         <v>63.59999847412109</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>36.63021087646484</v>
+        <v>36.63022613525391</v>
       </c>
       <c r="C20" t="n">
         <v>60.56999969482422</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.9680290222168</v>
+        <v>39.96801376342773</v>
       </c>
       <c r="C21" t="n">
         <v>65.93000030517578</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>37.19760513305664</v>
+        <v>37.19760894775391</v>
       </c>
       <c r="C23" t="n">
         <v>61.36000061035156</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.38831520080566</v>
+        <v>30.3883056640625</v>
       </c>
       <c r="C25" t="n">
         <v>50</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>33.68240737915039</v>
+        <v>33.68239974975586</v>
       </c>
       <c r="C26" t="n">
         <v>55.41999816894531</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>32.05904006958008</v>
+        <v>32.05904388427734</v>
       </c>
       <c r="C27" t="n">
         <v>52.61000061035156</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.88295745849609</v>
+        <v>30.88296699523926</v>
       </c>
       <c r="C28" t="n">
         <v>50.68000030517578</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>32.37591552734375</v>
+        <v>32.37590789794922</v>
       </c>
       <c r="C29" t="n">
         <v>53.13000106811523</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.59889984130859</v>
+        <v>32.5988883972168</v>
       </c>
       <c r="C30" t="n">
         <v>53.36000061035156</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.4018440246582</v>
+        <v>28.40185928344727</v>
       </c>
       <c r="C31" t="n">
         <v>46.4900016784668</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.6320915222168</v>
+        <v>27.63208961486816</v>
       </c>
       <c r="C32" t="n">
         <v>45.22999954223633</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>32.49232864379883</v>
+        <v>32.49232482910156</v>
       </c>
       <c r="C33" t="n">
         <v>53.02000045776367</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>30.05938911437988</v>
+        <v>30.05937576293945</v>
       </c>
       <c r="C34" t="n">
         <v>49.04999923706055</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.5868034362793</v>
+        <v>24.58678817749023</v>
       </c>
       <c r="C35" t="n">
         <v>40.11999893188477</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.79421615600586</v>
+        <v>20.7942008972168</v>
       </c>
       <c r="C36" t="n">
         <v>33.7599983215332</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.26849174499512</v>
+        <v>21.26849365234375</v>
       </c>
       <c r="C37" t="n">
         <v>34.52999877929688</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.21739959716797</v>
+        <v>19.21740341186523</v>
       </c>
       <c r="C38" t="n">
         <v>31.20000076293945</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>21.29726409912109</v>
+        <v>21.2972583770752</v>
       </c>
       <c r="C40" t="n">
         <v>34.38999938964844</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>25.5517635345459</v>
+        <v>25.55175590515137</v>
       </c>
       <c r="C41" t="n">
         <v>41.2599983215332</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.54050064086914</v>
+        <v>24.54050445556641</v>
       </c>
       <c r="C43" t="n">
         <v>39.47000122070312</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>27.12075614929199</v>
+        <v>27.12076568603516</v>
       </c>
       <c r="C44" t="n">
         <v>43.61999893188477</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.34282112121582</v>
+        <v>29.34283065795898</v>
       </c>
       <c r="C45" t="n">
         <v>47</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>29.14305686950684</v>
+        <v>29.14304733276367</v>
       </c>
       <c r="C46" t="n">
         <v>46.68000030517578</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.23560523986816</v>
+        <v>30.235595703125</v>
       </c>
       <c r="C47" t="n">
         <v>48.43000030517578</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.16980743408203</v>
+        <v>29.1698055267334</v>
       </c>
       <c r="C48" t="n">
         <v>46.56000137329102</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>30.30377578735352</v>
+        <v>30.30376243591309</v>
       </c>
       <c r="C49" t="n">
         <v>48.36999893188477</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>32.12062072753906</v>
+        <v>32.12060546875</v>
       </c>
       <c r="C50" t="n">
         <v>51.27000045776367</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.38715362548828</v>
+        <v>32.38717651367188</v>
       </c>
       <c r="C51" t="n">
         <v>51.52000045776367</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>33.06608200073242</v>
+        <v>33.06609344482422</v>
       </c>
       <c r="C52" t="n">
         <v>52.59999847412109</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>35.75034332275391</v>
+        <v>35.75035095214844</v>
       </c>
       <c r="C53" t="n">
         <v>56.86999893188477</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>34.38363265991211</v>
+        <v>34.38362884521484</v>
       </c>
       <c r="C54" t="n">
         <v>54.52999877929688</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.00390625</v>
+        <v>31.00389671325684</v>
       </c>
       <c r="C55" t="n">
         <v>49.16999816894531</v>
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.41782379150391</v>
+        <v>32.41781616210938</v>
       </c>
       <c r="C57" t="n">
         <v>51.15999984741211</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>33.8625602722168</v>
+        <v>33.86255645751953</v>
       </c>
       <c r="C58" t="n">
         <v>53.43999862670898</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>32.91207122802734</v>
+        <v>32.91208267211914</v>
       </c>
       <c r="C59" t="n">
         <v>51.93999862670898</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>36.24882888793945</v>
+        <v>36.24882507324219</v>
       </c>
       <c r="C60" t="n">
         <v>56.93999862670898</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.27964401245117</v>
+        <v>38.27963256835938</v>
       </c>
       <c r="C61" t="n">
         <v>60.13000106811523</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.90558242797852</v>
+        <v>34.90557098388672</v>
       </c>
       <c r="C62" t="n">
         <v>54.83000183105469</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>33.60857009887695</v>
+        <v>33.60855102539062</v>
       </c>
       <c r="C63" t="n">
         <v>52.54999923706055</v>
@@ -1774,7 +1786,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>31.402099609375</v>
+        <v>31.4020938873291</v>
       </c>
       <c r="C65" t="n">
         <v>49.09999847412109</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>31.83157539367676</v>
+        <v>31.83158874511719</v>
       </c>
       <c r="C66" t="n">
         <v>49.52999877929688</v>
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.14777946472168</v>
+        <v>30.14778709411621</v>
       </c>
       <c r="C67" t="n">
         <v>46.90999984741211</v>
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>33.09122085571289</v>
+        <v>33.09121322631836</v>
       </c>
       <c r="C68" t="n">
         <v>51.4900016784668</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>33.4139289855957</v>
+        <v>33.41390609741211</v>
       </c>
       <c r="C69" t="n">
         <v>51.66999816894531</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.71316719055176</v>
+        <v>31.71315383911133</v>
       </c>
       <c r="C70" t="n">
         <v>49.04000091552734</v>
@@ -1977,7 +1989,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>34.27375030517578</v>
+        <v>34.27373886108398</v>
       </c>
       <c r="C72" t="n">
         <v>52.70000076293945</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.31121063232422</v>
+        <v>33.31122589111328</v>
       </c>
       <c r="C73" t="n">
         <v>51.22000122070312</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>33.04458236694336</v>
+        <v>33.04457473754883</v>
       </c>
       <c r="C74" t="n">
         <v>50.81000137329102</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>37.08082580566406</v>
+        <v>37.08083343505859</v>
       </c>
       <c r="C75" t="n">
         <v>56.68999862670898</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>38.11432266235352</v>
+        <v>38.11433029174805</v>
       </c>
       <c r="C76" t="n">
         <v>58.27000045776367</v>
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>37.89846038818359</v>
+        <v>37.89846420288086</v>
       </c>
       <c r="C77" t="n">
         <v>57.93999862670898</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>38.08497619628906</v>
+        <v>38.08496475219727</v>
       </c>
       <c r="C78" t="n">
         <v>57.90999984741211</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.26910018920898</v>
+        <v>38.26910781860352</v>
       </c>
       <c r="C79" t="n">
         <v>58.18999862670898</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>39.88695526123047</v>
+        <v>39.88693618774414</v>
       </c>
       <c r="C80" t="n">
         <v>60.65000152587891</v>
@@ -2267,7 +2279,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.98204803466797</v>
+        <v>41.9820442199707</v>
       </c>
       <c r="C82" t="n">
         <v>63.47000122070312</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>42.16725921630859</v>
+        <v>42.16726303100586</v>
       </c>
       <c r="C83" t="n">
         <v>63.75</v>
@@ -2354,7 +2366,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2383,7 +2395,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.18952941894531</v>
+        <v>40.18950653076172</v>
       </c>
       <c r="C86" t="n">
         <v>60.40999984741211</v>
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>42.12636566162109</v>
+        <v>42.12635803222656</v>
       </c>
       <c r="C87" t="n">
         <v>62.95999908447266</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>45.79970550537109</v>
+        <v>45.79970169067383</v>
       </c>
       <c r="C88" t="n">
         <v>68.44999694824219</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>47.21149444580078</v>
+        <v>47.21149826049805</v>
       </c>
       <c r="C89" t="n">
         <v>70.55999755859375</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>46.74354553222656</v>
+        <v>46.7435417175293</v>
       </c>
       <c r="C90" t="n">
         <v>69.5</v>
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>46.31310272216797</v>
+        <v>46.3130989074707</v>
       </c>
       <c r="C91" t="n">
         <v>68.86000061035156</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>47.92053985595703</v>
+        <v>47.9205322265625</v>
       </c>
       <c r="C92" t="n">
         <v>71.25</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.8489990234375</v>
+        <v>42.8490104675293</v>
       </c>
       <c r="C93" t="n">
         <v>63.31000137329102</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.30245971679688</v>
+        <v>43.30248641967773</v>
       </c>
       <c r="C94" t="n">
         <v>63.97999954223633</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.85068893432617</v>
+        <v>43.85070037841797</v>
       </c>
       <c r="C95" t="n">
         <v>64.79000091552734</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>43.548583984375</v>
+        <v>43.54859161376953</v>
       </c>
       <c r="C96" t="n">
         <v>63.93000030517578</v>
@@ -2731,7 +2743,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>38.58270263671875</v>
+        <v>38.58270645141602</v>
       </c>
       <c r="C98" t="n">
         <v>56.63999938964844</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>42.92636108398438</v>
+        <v>42.92635345458984</v>
       </c>
       <c r="C99" t="n">
         <v>62.54000091552734</v>
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>41.53300476074219</v>
+        <v>41.53298950195312</v>
       </c>
       <c r="C100" t="n">
         <v>60.5099983215332</v>
@@ -2847,7 +2859,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>39.24684906005859</v>
+        <v>39.24686050415039</v>
       </c>
       <c r="C102" t="n">
         <v>56.7599983215332</v>
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>40.06968688964844</v>
+        <v>40.06968307495117</v>
       </c>
       <c r="C103" t="n">
         <v>57.95000076293945</v>
@@ -2934,11 +2946,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>41.20367431640625</v>
+        <v>41.20366287231445</v>
       </c>
       <c r="C104" t="n">
         <v>59.59000015258789</v>
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>41.91002655029297</v>
+        <v>41.91001892089844</v>
       </c>
       <c r="C105" t="n">
         <v>60.06999969482422</v>
@@ -2992,7 +3004,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>43.13097381591797</v>
+        <v>43.13096618652344</v>
       </c>
       <c r="C107" t="n">
         <v>61.81999969482422</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.02588272094727</v>
+        <v>52.02587127685547</v>
       </c>
       <c r="C108" t="n">
         <v>74</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.36871719360352</v>
+        <v>53.36872100830078</v>
       </c>
       <c r="C109" t="n">
         <v>75.91000366210938</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>51.75168991088867</v>
+        <v>51.75169372558594</v>
       </c>
       <c r="C110" t="n">
         <v>73.61000061035156</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.38340759277344</v>
+        <v>54.38340377807617</v>
       </c>
       <c r="C111" t="n">
         <v>76.83000183105469</v>
@@ -3166,11 +3178,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>58.09249877929688</v>
+        <v>58.09248733520508</v>
       </c>
       <c r="C112" t="n">
         <v>82.06999969482422</v>
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.799072265625</v>
+        <v>55.7990837097168</v>
       </c>
       <c r="C113" t="n">
         <v>78.83000183105469</v>
@@ -3220,11 +3232,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.52018737792969</v>
+        <v>56.52017593383789</v>
       </c>
       <c r="C114" t="n">
         <v>79.31999969482422</v>
@@ -3247,11 +3259,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>58.16619873046875</v>
+        <v>58.16618728637695</v>
       </c>
       <c r="C115" t="n">
         <v>81.62999725341797</v>
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>58.32296752929688</v>
+        <v>58.32296371459961</v>
       </c>
       <c r="C116" t="n">
         <v>81.84999847412109</v>
@@ -3301,11 +3313,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>55.76654052734375</v>
+        <v>55.76652526855469</v>
       </c>
       <c r="C117" t="n">
         <v>77.70999908447266</v>
@@ -3328,11 +3340,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>56.44827270507812</v>
+        <v>56.44826889038086</v>
       </c>
       <c r="C118" t="n">
         <v>78.66000366210938</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>55.38618087768555</v>
+        <v>55.38619995117188</v>
       </c>
       <c r="C119" t="n">
         <v>77.18000030517578</v>
@@ -3382,11 +3394,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>52.43616485595703</v>
+        <v>52.43616104125977</v>
       </c>
       <c r="C120" t="n">
         <v>72.5</v>
@@ -3409,11 +3421,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>52.51572036743164</v>
+        <v>52.51572799682617</v>
       </c>
       <c r="C121" t="n">
         <v>72.61000061035156</v>
@@ -3436,11 +3448,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>52.3783073425293</v>
+        <v>52.37830352783203</v>
       </c>
       <c r="C122" t="n">
         <v>72.41999816894531</v>
@@ -3463,11 +3475,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>57.21034240722656</v>
+        <v>57.21035766601562</v>
       </c>
       <c r="C123" t="n">
         <v>78.44999694824219</v>
@@ -3490,11 +3502,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.00341033935547</v>
+        <v>60.0034065246582</v>
       </c>
       <c r="C124" t="n">
         <v>82.27999877929688</v>
@@ -3519,11 +3531,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>57.97607421875</v>
+        <v>57.97607803344727</v>
       </c>
       <c r="C125" t="n">
         <v>79.5</v>
@@ -3548,11 +3560,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.54151153564453</v>
+        <v>50.54150772094727</v>
       </c>
       <c r="C126" t="n">
         <v>68.77999877929688</v>
@@ -3577,11 +3589,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.30573272705078</v>
+        <v>51.30572891235352</v>
       </c>
       <c r="C127" t="n">
         <v>69.81999969482422</v>
@@ -3606,11 +3618,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>55.35462951660156</v>
+        <v>55.35466003417969</v>
       </c>
       <c r="C128" t="n">
         <v>75.33000183105469</v>
@@ -3635,11 +3647,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>51.98909378051758</v>
+        <v>51.98909759521484</v>
       </c>
       <c r="C129" t="n">
         <v>70.19000244140625</v>
@@ -3664,11 +3676,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>50.87066650390625</v>
+        <v>50.87065505981445</v>
       </c>
       <c r="C130" t="n">
         <v>68.68000030517578</v>
@@ -3693,11 +3705,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>50.90769577026367</v>
+        <v>50.90767669677734</v>
       </c>
       <c r="C131" t="n">
         <v>68.73000335693359</v>
@@ -3722,11 +3734,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.69615173339844</v>
+        <v>57.69614028930664</v>
       </c>
       <c r="C132" t="n">
         <v>77.23999786376953</v>
@@ -3751,11 +3763,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>53.95381927490234</v>
+        <v>53.95380401611328</v>
       </c>
       <c r="C133" t="n">
         <v>72.23000335693359</v>
@@ -3780,7 +3792,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3809,11 +3821,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.30398559570312</v>
+        <v>44.30398941040039</v>
       </c>
       <c r="C135" t="n">
         <v>58.77000045776367</v>
@@ -3838,11 +3850,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>41.60518264770508</v>
+        <v>41.60519409179688</v>
       </c>
       <c r="C136" t="n">
         <v>55.18999862670898</v>
@@ -3867,7 +3879,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3896,7 +3908,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3925,11 +3937,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>39.84748458862305</v>
+        <v>39.84749221801758</v>
       </c>
       <c r="C139" t="n">
         <v>52.29000091552734</v>
@@ -3954,11 +3966,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>43.18524551391602</v>
+        <v>43.18524932861328</v>
       </c>
       <c r="C140" t="n">
         <v>56.66999816894531</v>
@@ -3983,11 +3995,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>42.02264404296875</v>
+        <v>42.02264022827148</v>
       </c>
       <c r="C141" t="n">
         <v>54.52999877929688</v>
@@ -4012,7 +4024,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>45.49819946289062</v>
+        <v>45.49820709228516</v>
       </c>
       <c r="C143" t="n">
         <v>59.04000091552734</v>
@@ -4070,11 +4082,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>46.63969802856445</v>
+        <v>46.63969421386719</v>
       </c>
       <c r="C144" t="n">
         <v>59.90000152587891</v>
@@ -4099,7 +4111,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4128,11 +4140,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>58.56826782226562</v>
+        <v>58.56824493408203</v>
       </c>
       <c r="C146" t="n">
         <v>75.22000122070312</v>
@@ -4157,11 +4169,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>59.20105361938477</v>
+        <v>59.20107650756836</v>
       </c>
       <c r="C147" t="n">
         <v>75.41000366210938</v>
@@ -4186,11 +4198,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>54.50642395019531</v>
+        <v>54.50642776489258</v>
       </c>
       <c r="C148" t="n">
         <v>69.43000030517578</v>
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>56.99504089355469</v>
+        <v>56.99505615234375</v>
       </c>
       <c r="C149" t="n">
         <v>72.59999847412109</v>
@@ -4244,11 +4256,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>57.71355056762695</v>
+        <v>57.71358489990234</v>
       </c>
       <c r="C150" t="n">
         <v>72.88999938964844</v>
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>60.27103805541992</v>
+        <v>60.27103042602539</v>
       </c>
       <c r="C151" t="n">
         <v>76.12000274658203</v>
@@ -4302,11 +4314,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>63.88162231445312</v>
+        <v>63.88159561157227</v>
       </c>
       <c r="C152" t="n">
         <v>80.68000030517578</v>
@@ -4331,11 +4343,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>69.82621002197266</v>
+        <v>69.82619476318359</v>
       </c>
       <c r="C153" t="n">
         <v>87.5</v>
@@ -4360,11 +4372,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>70.39279174804688</v>
+        <v>70.39278411865234</v>
       </c>
       <c r="C154" t="n">
         <v>88.20999908447266</v>
@@ -4389,11 +4401,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>66.73786926269531</v>
+        <v>66.73786163330078</v>
       </c>
       <c r="C155" t="n">
         <v>83.62999725341797</v>
@@ -4418,7 +4430,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4447,7 +4459,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4476,11 +4488,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>58.73824691772461</v>
+        <v>58.73825454711914</v>
       </c>
       <c r="C158" t="n">
         <v>73</v>
@@ -4505,11 +4517,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>58.96669387817383</v>
+        <v>58.9666862487793</v>
       </c>
       <c r="C159" t="n">
         <v>72.63999938964844</v>
@@ -4534,11 +4546,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>65.15233612060547</v>
+        <v>65.15232849121094</v>
       </c>
       <c r="C160" t="n">
         <v>80.26000213623047</v>
@@ -4563,11 +4575,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>62.8469352722168</v>
+        <v>62.84692764282227</v>
       </c>
       <c r="C161" t="n">
         <v>77.41999816894531</v>
@@ -4592,11 +4604,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>65.89492797851562</v>
+        <v>65.89493560791016</v>
       </c>
       <c r="C162" t="n">
         <v>80.44999694824219</v>
@@ -4621,11 +4633,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>70.94047546386719</v>
+        <v>70.94044494628906</v>
       </c>
       <c r="C163" t="n">
         <v>86.61000061035156</v>
@@ -4650,11 +4662,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>70.76845550537109</v>
+        <v>70.76846313476562</v>
       </c>
       <c r="C164" t="n">
         <v>86.40000152587891</v>
@@ -4679,11 +4691,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>88.34772491455078</v>
+        <v>88.34771728515625</v>
       </c>
       <c r="C165" t="n">
         <v>107.0400009155273</v>
@@ -4708,11 +4720,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>88.24044799804688</v>
+        <v>88.24044036865234</v>
       </c>
       <c r="C166" t="n">
         <v>106.9100036621094</v>
@@ -4737,11 +4749,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>88.24044799804688</v>
+        <v>88.24044036865234</v>
       </c>
       <c r="C167" t="n">
         <v>106.9100036621094</v>
@@ -4766,11 +4778,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>103.7914886474609</v>
+        <v>103.79150390625</v>
       </c>
       <c r="C168" t="n">
         <v>125.0100021362305</v>
@@ -4795,11 +4807,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>106.4483489990234</v>
+        <v>106.448356628418</v>
       </c>
       <c r="C169" t="n">
         <v>128.2100067138672</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>91.94361877441406</v>
+        <v>91.94361114501953</v>
       </c>
       <c r="C170" t="n">
         <v>110.7399978637695</v>
@@ -4853,11 +4865,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>86.00403594970703</v>
+        <v>86.0040283203125</v>
       </c>
       <c r="C171" t="n">
         <v>103</v>
@@ -4882,11 +4894,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>77.62908172607422</v>
+        <v>77.62906646728516</v>
       </c>
       <c r="C172" t="n">
         <v>92.97000122070312</v>
@@ -4911,11 +4923,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>91.63187408447266</v>
+        <v>91.63188934326172</v>
       </c>
       <c r="C173" t="n">
         <v>109.7399978637695</v>
@@ -4940,11 +4952,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>102.6857147216797</v>
+        <v>102.6857299804688</v>
       </c>
       <c r="C174" t="n">
         <v>122.3300018310547</v>
@@ -4969,11 +4981,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>100.6711349487305</v>
+        <v>100.6711120605469</v>
       </c>
       <c r="C175" t="n">
         <v>119.9300003051758</v>
@@ -4998,11 +5010,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>105.6656494140625</v>
+        <v>105.6656265258789</v>
       </c>
       <c r="C176" t="n">
         <v>125.879997253418</v>
@@ -5027,11 +5039,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.5554580688477</v>
+        <v>127.5554733276367</v>
       </c>
       <c r="C177" t="n">
         <v>151.2100067138672</v>
@@ -5056,7 +5068,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5085,11 +5097,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>128.4074554443359</v>
+        <v>128.4075012207031</v>
       </c>
       <c r="C179" t="n">
         <v>152.2200012207031</v>
@@ -5114,11 +5126,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>152.0713195800781</v>
+        <v>152.0713043212891</v>
       </c>
       <c r="C180" t="n">
         <v>179.5299987792969</v>
@@ -5143,11 +5155,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>149.5301055908203</v>
+        <v>149.5301513671875</v>
       </c>
       <c r="C181" t="n">
         <v>176.5299987792969</v>
@@ -5172,11 +5184,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>153.4604339599609</v>
+        <v>153.4604644775391</v>
       </c>
       <c r="C182" t="n">
         <v>181.1699981689453</v>
@@ -5201,11 +5213,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>155.9371643066406</v>
+        <v>155.9371795654297</v>
       </c>
       <c r="C183" t="n">
         <v>183.4400024414062</v>
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>168.3737487792969</v>
+        <v>168.3737182617188</v>
       </c>
       <c r="C184" t="n">
         <v>198.0700073242188</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>176.1858825683594</v>
+        <v>176.1858978271484</v>
       </c>
       <c r="C185" t="n">
         <v>207.2599945068359</v>
@@ -5288,7 +5300,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5317,7 +5329,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5346,11 +5358,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>222.6320953369141</v>
+        <v>222.6320648193359</v>
       </c>
       <c r="C188" t="n">
         <v>261.0499877929688</v>
@@ -5375,11 +5387,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>211.3556365966797</v>
+        <v>211.3556060791016</v>
       </c>
       <c r="C189" t="n">
         <v>246.9799957275391</v>
@@ -5404,11 +5416,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>195.7721862792969</v>
+        <v>195.772216796875</v>
       </c>
       <c r="C190" t="n">
         <v>228.7700042724609</v>
@@ -5433,11 +5445,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>222.17236328125</v>
+        <v>222.1723785400391</v>
       </c>
       <c r="C191" t="n">
         <v>259.6199951171875</v>
@@ -5462,11 +5474,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>209.3814392089844</v>
+        <v>209.3814086914062</v>
       </c>
       <c r="C192" t="n">
         <v>243.8399963378906</v>
@@ -5491,7 +5503,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5520,11 +5532,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>189.2796478271484</v>
+        <v>189.2796325683594</v>
       </c>
       <c r="C194" t="n">
         <v>220.4299926757812</v>
@@ -5549,11 +5561,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>172.2826232910156</v>
+        <v>172.2826538085938</v>
       </c>
       <c r="C195" t="n">
         <v>199.7700042724609</v>
@@ -5578,11 +5590,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>183.0196075439453</v>
+        <v>183.0195922851562</v>
       </c>
       <c r="C196" t="n">
         <v>212.2200012207031</v>
@@ -5607,11 +5619,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>197.1888580322266</v>
+        <v>197.1888732910156</v>
       </c>
       <c r="C197" t="n">
         <v>228.6499938964844</v>
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>140.1815490722656</v>
+        <v>140.1815643310547</v>
       </c>
       <c r="C198" t="n">
         <v>161.8800048828125</v>
@@ -5665,11 +5677,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>122.2994689941406</v>
+        <v>122.2994537353516</v>
       </c>
       <c r="C199" t="n">
         <v>141.2299957275391</v>
@@ -5694,11 +5706,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>141.4804992675781</v>
+        <v>141.4805145263672</v>
       </c>
       <c r="C200" t="n">
         <v>163.3800048828125</v>
@@ -5723,7 +5735,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>129.3051605224609</v>
+        <v>129.3052062988281</v>
       </c>
       <c r="C202" t="n">
         <v>148.3899993896484</v>
@@ -5781,11 +5793,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>143.1253662109375</v>
+        <v>143.1253814697266</v>
       </c>
       <c r="C203" t="n">
         <v>164.25</v>
@@ -5810,11 +5822,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>146.4958801269531</v>
+        <v>146.495849609375</v>
       </c>
       <c r="C204" t="n">
         <v>167.0700073242188</v>
@@ -5839,7 +5851,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5868,7 +5880,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>148.6761779785156</v>
+        <v>148.6761932373047</v>
       </c>
       <c r="C207" t="n">
         <v>168.5</v>
@@ -5926,11 +5938,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>146.1438293457031</v>
+        <v>146.1438598632812</v>
       </c>
       <c r="C208" t="n">
         <v>165.6300048828125</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>139.1909027099609</v>
+        <v>139.1908874511719</v>
       </c>
       <c r="C209" t="n">
         <v>157.75</v>
@@ -5984,7 +5996,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6013,11 +6025,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>117.1702117919922</v>
+        <v>117.1702194213867</v>
       </c>
       <c r="C211" t="n">
         <v>131.8999938964844</v>
@@ -6042,11 +6054,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>121.229850769043</v>
+        <v>121.2298812866211</v>
       </c>
       <c r="C212" t="n">
         <v>136.4700012207031</v>
@@ -6071,7 +6083,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6100,11 +6112,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>99.06420135498047</v>
+        <v>99.06421661376953</v>
       </c>
       <c r="C214" t="n">
         <v>110.5699996948242</v>
@@ -6129,11 +6141,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>99.26132202148438</v>
+        <v>99.26131439208984</v>
       </c>
       <c r="C215" t="n">
         <v>110.7900009155273</v>
@@ -6158,11 +6170,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.1276397705078</v>
+        <v>121.1276550292969</v>
       </c>
       <c r="C216" t="n">
         <v>133.8099975585938</v>
@@ -6187,11 +6199,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>128.9216156005859</v>
+        <v>128.9216003417969</v>
       </c>
       <c r="C217" t="n">
         <v>142.4199981689453</v>
@@ -6216,11 +6228,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>125.8981857299805</v>
+        <v>125.8981552124023</v>
       </c>
       <c r="C218" t="n">
         <v>139.0800018310547</v>
@@ -6245,11 +6257,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>139.4517364501953</v>
+        <v>139.4517517089844</v>
       </c>
       <c r="C219" t="n">
         <v>152.9199981689453</v>
@@ -6274,7 +6286,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6303,7 +6315,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6332,11 +6344,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>143.3866424560547</v>
+        <v>143.3866577148438</v>
       </c>
       <c r="C222" t="n">
         <v>156.1600036621094</v>
@@ -6361,11 +6373,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>135.9308319091797</v>
+        <v>135.9308471679688</v>
       </c>
       <c r="C223" t="n">
         <v>148.0399932861328</v>
@@ -6390,7 +6402,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6419,11 +6431,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>142.1575164794922</v>
+        <v>142.1575317382812</v>
       </c>
       <c r="C225" t="n">
         <v>153.6199951171875</v>
@@ -6448,11 +6460,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>144.2304229736328</v>
+        <v>144.2304077148438</v>
       </c>
       <c r="C226" t="n">
         <v>155.8600006103516</v>
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6506,11 +6518,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>123.3230133056641</v>
+        <v>123.322998046875</v>
       </c>
       <c r="C228" t="n">
         <v>132.3099975585938</v>
@@ -6535,11 +6547,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>125.998046875</v>
+        <v>125.9980392456055</v>
       </c>
       <c r="C229" t="n">
         <v>135.1799926757812</v>
@@ -6564,7 +6576,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6593,7 +6605,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6622,11 +6634,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>98.10102081298828</v>
+        <v>98.10100555419922</v>
       </c>
       <c r="C232" t="n">
         <v>104.3600006103516</v>
@@ -6651,11 +6663,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>90.90042877197266</v>
+        <v>90.90042114257812</v>
       </c>
       <c r="C233" t="n">
         <v>96.69999694824219</v>
@@ -6680,11 +6692,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>89.38201904296875</v>
+        <v>89.38202667236328</v>
       </c>
       <c r="C234" t="n">
         <v>94.01000213623047</v>
@@ -6709,11 +6721,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>93.79360961914062</v>
+        <v>93.79361724853516</v>
       </c>
       <c r="C235" t="n">
         <v>98.65000152587891</v>
@@ -6738,11 +6750,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>95.55252838134766</v>
+        <v>95.55253601074219</v>
       </c>
       <c r="C236" t="n">
         <v>100.5</v>
@@ -6767,7 +6779,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6825,11 +6837,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>89.11156463623047</v>
+        <v>89.11155700683594</v>
       </c>
       <c r="C239" t="n">
         <v>92.72000122070312</v>
@@ -6854,11 +6866,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>88.19110107421875</v>
+        <v>88.19110870361328</v>
       </c>
       <c r="C240" t="n">
         <v>90.62000274658203</v>
@@ -6883,11 +6895,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>95.12999725341797</v>
+        <v>95.12998962402344</v>
       </c>
       <c r="C241" t="n">
         <v>97.75</v>
@@ -6912,7 +6924,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6941,7 +6953,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6970,7 +6982,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6999,7 +7011,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7057,7 +7069,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7086,7 +7098,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7115,7 +7127,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7144,32 +7156,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>156.2599945068359</v>
+        <v>156.1499938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>156.2599945068359</v>
+        <v>156.1499938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>51541400</v>
+        <v>54888900</v>
       </c>
       <c r="E250" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>16.22637533819688</v>
+        <v>16.21495263722579</v>
       </c>
       <c r="G250" t="n">
         <v>454296736</v>
       </c>
       <c r="H250" t="n">
-        <v>70988405471.8335</v>
+        <v>70938432553.59277</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1134531593905178</v>
+        <v>0.1208216913097082</v>
       </c>
     </row>
   </sheetData>
@@ -7201,75 +7213,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39572</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39662</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39663</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39753</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39935</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39936</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7431,13 +7443,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40027</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7473,13 +7485,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7506,7 +7518,7 @@
       <c r="I7" t="n">
         <v>3.3</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K7" t="n">
@@ -7519,13 +7531,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7552,7 +7564,7 @@
       <c r="I8" t="n">
         <v>3.51</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K8" t="n">
@@ -7565,13 +7577,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7598,7 +7610,7 @@
       <c r="I9" t="n">
         <v>3.64</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K9" t="n">
@@ -7611,13 +7623,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40515</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7644,7 +7656,7 @@
       <c r="I10" t="n">
         <v>3.8</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K10" t="n">
@@ -7657,13 +7669,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7690,7 +7702,7 @@
       <c r="I11" t="n">
         <v>4.01</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K11" t="n">
@@ -7703,13 +7715,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7736,7 +7748,7 @@
       <c r="I12" t="n">
         <v>4.1</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="K12" t="n">
@@ -7749,13 +7761,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7782,7 +7794,7 @@
       <c r="I13" t="n">
         <v>4.21</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="K13" t="n">
@@ -7795,13 +7807,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7828,7 +7840,7 @@
       <c r="I14" t="n">
         <v>4.29</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="K14" t="n">
@@ -7841,13 +7853,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40936</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7874,7 +7886,7 @@
       <c r="I15" t="n">
         <v>4.289999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="K15" t="n">
@@ -7887,13 +7899,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41027</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7920,7 +7932,7 @@
       <c r="I16" t="n">
         <v>4.34</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="K16" t="n">
@@ -7933,13 +7945,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41118</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7966,7 +7978,7 @@
       <c r="I17" t="n">
         <v>4.369999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="K17" t="n">
@@ -7979,13 +7991,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41209</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8012,7 +8024,7 @@
       <c r="I18" t="n">
         <v>4.51</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="K18" t="n">
@@ -8025,13 +8037,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41307</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8058,7 +8070,7 @@
       <c r="I19" t="n">
         <v>4.53</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="K19" t="n">
@@ -8071,13 +8083,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41308</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41398</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8104,7 +8116,7 @@
       <c r="I20" t="n">
         <v>4.26</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="K20" t="n">
@@ -8117,13 +8129,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41399</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41489</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8150,7 +8162,7 @@
       <c r="I21" t="n">
         <v>4.15</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="K21" t="n">
@@ -8163,13 +8175,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41490</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41580</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8196,7 +8208,7 @@
       <c r="I22" t="n">
         <v>3.73</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="K22" t="n">
@@ -8209,13 +8221,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41581</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8242,7 +8254,7 @@
       <c r="I23" t="n">
         <v>3.07</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="K23" t="n">
@@ -8255,13 +8267,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41672</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41762</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8288,7 +8300,7 @@
       <c r="I24" t="n">
         <v>2.96</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="K24" t="n">
@@ -8301,13 +8313,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41763</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41853</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8334,7 +8346,7 @@
       <c r="I25" t="n">
         <v>2.38</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="K25" t="n">
@@ -8347,13 +8359,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41854</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8380,7 +8392,7 @@
       <c r="I26" t="n">
         <v>2.39</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="K26" t="n">
@@ -8393,13 +8405,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41945</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8426,7 +8438,7 @@
       <c r="I27" t="n">
         <v>-2.52</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="K27" t="n">
@@ -8439,13 +8451,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42126</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8472,7 +8484,7 @@
       <c r="I28" t="n">
         <v>-2.2</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="K28" t="n">
@@ -8485,13 +8497,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42127</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8518,7 +8530,7 @@
       <c r="I29" t="n">
         <v>-1.389999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="K29" t="n">
@@ -8531,13 +8543,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42218</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8564,7 +8576,7 @@
       <c r="I30" t="n">
         <v>-1.07</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="K30" t="n">
@@ -8577,13 +8589,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42399</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8610,7 +8622,7 @@
       <c r="I31" t="n">
         <v>5.35</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="K31" t="n">
@@ -8623,13 +8635,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8656,7 +8668,7 @@
       <c r="I32" t="n">
         <v>5.419999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="K32" t="n">
@@ -8669,13 +8681,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42581</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42606</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8702,7 +8714,7 @@
       <c r="I33" t="n">
         <v>5.399999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42606</v>
       </c>
       <c r="K33" t="n">
@@ -8715,13 +8727,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42672</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8748,7 +8760,7 @@
       <c r="I34" t="n">
         <v>5.59</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="K34" t="n">
@@ -8761,13 +8773,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42763</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42802</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8794,7 +8806,7 @@
       <c r="I35" t="n">
         <v>4.72</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42802</v>
       </c>
       <c r="K35" t="n">
@@ -8807,13 +8819,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42854</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8840,7 +8852,7 @@
       <c r="I36" t="n">
         <v>4.9</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="K36" t="n">
@@ -8853,13 +8865,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42945</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42968</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8886,7 +8898,7 @@
       <c r="I37" t="n">
         <v>4.96</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42968</v>
       </c>
       <c r="K37" t="n">
@@ -8899,13 +8911,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43036</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8932,7 +8944,7 @@
       <c r="I38" t="n">
         <v>4.78</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="K38" t="n">
@@ -8945,13 +8957,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43134</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43173</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8978,7 +8990,7 @@
       <c r="I39" t="n">
         <v>5.35</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43173</v>
       </c>
       <c r="K39" t="n">
@@ -8991,13 +9003,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43135</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43225</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43249</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9024,7 +9036,7 @@
       <c r="I40" t="n">
         <v>5.45</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43249</v>
       </c>
       <c r="K40" t="n">
@@ -9037,13 +9049,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43226</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43316</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43339</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9070,7 +9082,7 @@
       <c r="I41" t="n">
         <v>5.720000000000001</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43339</v>
       </c>
       <c r="K41" t="n">
@@ -9083,13 +9095,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43317</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43407</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43431</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9116,7 +9128,7 @@
       <c r="I42" t="n">
         <v>6.01</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43431</v>
       </c>
       <c r="K42" t="n">
@@ -9129,13 +9141,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43408</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43498</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9162,7 +9174,7 @@
       <c r="I43" t="n">
         <v>5.51</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K43" t="n">
@@ -9175,13 +9187,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43499</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43589</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9208,7 +9220,7 @@
       <c r="I44" t="n">
         <v>5.71</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="K44" t="n">
@@ -9221,13 +9233,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43590</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9254,7 +9266,7 @@
       <c r="I45" t="n">
         <v>6.04</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="K45" t="n">
@@ -9267,13 +9279,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43681</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43771</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9300,7 +9312,7 @@
       <c r="I46" t="n">
         <v>6.26</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="K46" t="n">
@@ -9313,13 +9325,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43772</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43901</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9346,7 +9358,7 @@
       <c r="I47" t="n">
         <v>6.37</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43901</v>
       </c>
       <c r="K47" t="n">
@@ -9359,13 +9371,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9392,7 +9404,7 @@
       <c r="I48" t="n">
         <v>5.4</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="K48" t="n">
@@ -9405,13 +9417,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9438,7 +9450,7 @@
       <c r="I49" t="n">
         <v>6.93</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="K49" t="n">
@@ -9451,13 +9463,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9484,7 +9496,7 @@
       <c r="I50" t="n">
         <v>7.55</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="K50" t="n">
@@ -9497,13 +9509,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9530,7 +9542,7 @@
       <c r="I51" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="K51" t="n">
@@ -9543,13 +9555,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9576,7 +9588,7 @@
       <c r="I52" t="n">
         <v>12.25</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="K52" t="n">
@@ -9589,13 +9601,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9622,7 +9634,7 @@
       <c r="I53" t="n">
         <v>12.55</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="K53" t="n">
@@ -9635,13 +9647,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9668,7 +9680,7 @@
       <c r="I54" t="n">
         <v>13.58</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="K54" t="n">
@@ -9681,13 +9693,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44629</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9714,7 +9726,7 @@
       <c r="I55" t="n">
         <v>14.1</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44629</v>
       </c>
       <c r="K55" t="n">
@@ -9727,13 +9739,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9760,7 +9772,7 @@
       <c r="I56" t="n">
         <v>12.09</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="K56" t="n">
@@ -9773,13 +9785,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9806,7 +9818,7 @@
       <c r="I57" t="n">
         <v>8.83</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="K57" t="n">
@@ -9819,13 +9831,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9852,7 +9864,7 @@
       <c r="I58" t="n">
         <v>7.330000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="K58" t="n">
@@ -9865,13 +9877,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44954</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9898,7 +9910,7 @@
       <c r="I59" t="n">
         <v>5.98</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="K59" t="n">
@@ -9911,13 +9923,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45045</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9944,7 +9956,7 @@
       <c r="I60" t="n">
         <v>5.870000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="K60" t="n">
@@ -9957,13 +9969,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45136</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9990,7 +10002,7 @@
       <c r="I61" t="n">
         <v>7.280000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="K61" t="n">
@@ -10003,13 +10015,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45227</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45252</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10036,7 +10048,7 @@
       <c r="I62" t="n">
         <v>7.84</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45252</v>
       </c>
       <c r="K62" t="n">
@@ -10049,13 +10061,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10082,7 +10094,7 @@
       <c r="I63" t="n">
         <v>8.94</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="K63" t="n">
@@ -10095,13 +10107,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45326</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45416</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10128,7 +10140,7 @@
       <c r="I64" t="n">
         <v>8.92</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="K64" t="n">
@@ -10141,13 +10153,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45417</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10174,7 +10186,7 @@
       <c r="I65" t="n">
         <v>9.69</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="K65" t="n">
@@ -10187,13 +10199,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45508</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45598</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10220,7 +10232,7 @@
       <c r="I66" t="n">
         <v>9.44</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="K66" t="n">
@@ -10233,13 +10245,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45599</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10266,7 +10278,7 @@
       <c r="I67" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="K67" t="n">
@@ -10279,13 +10291,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45780</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10312,7 +10324,7 @@
       <c r="I68" t="n">
         <v>9.100000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="K68" t="n">
@@ -10325,13 +10337,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45781</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10358,7 +10370,7 @@
       <c r="I69" t="n">
         <v>8.58</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="K69" t="n">
@@ -10371,13 +10383,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10404,7 +10416,7 @@
       <c r="I70" t="n">
         <v>8.24</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="K70" t="n">
@@ -10417,13 +10429,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10450,7 +10462,7 @@
       <c r="I71" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K71" t="n">
@@ -10463,13 +10475,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10496,7 +10508,7 @@
       <c r="I72" t="n">
         <v>7.57</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="K72" t="n">
@@ -10509,13 +10521,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46235</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10542,7 +10554,7 @@
       <c r="I73" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="K73" t="n">
@@ -10579,52 +10591,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40051</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40053</v>
       </c>
       <c r="C2" t="n">
@@ -10653,10 +10665,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40149</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="C3" t="n">
@@ -10685,10 +10697,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40247</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40249</v>
       </c>
       <c r="C4" t="n">
@@ -10717,10 +10729,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40324</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="C5" t="n">
@@ -10749,10 +10761,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40415</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40417</v>
       </c>
       <c r="C6" t="n">
@@ -10781,10 +10793,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40515</v>
       </c>
       <c r="C7" t="n">
@@ -10813,10 +10825,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40609</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="C8" t="n">
@@ -10845,10 +10857,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40686</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="C9" t="n">
@@ -10877,10 +10889,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40777</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="C10" t="n">
@@ -10909,10 +10921,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40865</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="C11" t="n">
@@ -10941,10 +10953,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40980</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="C12" t="n">
@@ -10973,10 +10985,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41047</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41052</v>
       </c>
       <c r="C13" t="n">
@@ -11005,10 +11017,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41141</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41144</v>
       </c>
       <c r="C14" t="n">
@@ -11037,10 +11049,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41229</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="C15" t="n">
@@ -11069,10 +11081,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41348</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="C16" t="n">
@@ -11101,10 +11113,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41422</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="C17" t="n">
@@ -11133,10 +11145,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41509</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="C18" t="n">
@@ -11165,10 +11177,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41600</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="C19" t="n">
@@ -11197,10 +11209,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41708</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="C20" t="n">
@@ -11229,10 +11241,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41782</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41788</v>
       </c>
       <c r="C21" t="n">
@@ -11261,10 +11273,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41873</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="C22" t="n">
@@ -11293,10 +11305,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41964</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="C23" t="n">
@@ -11325,10 +11337,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="C24" t="n">
@@ -11357,10 +11369,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42146</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42152</v>
       </c>
       <c r="C25" t="n">
@@ -11389,10 +11401,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42236</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="C26" t="n">
@@ -11421,10 +11433,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42327</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="C27" t="n">
@@ -11453,10 +11465,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42433</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="C28" t="n">
@@ -11485,10 +11497,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42509</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42515</v>
       </c>
       <c r="C29" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42600</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42606</v>
       </c>
       <c r="C30" t="n">
@@ -11549,10 +11561,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42691</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="C31" t="n">
@@ -11581,10 +11593,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42796</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42802</v>
       </c>
       <c r="C32" t="n">
@@ -11613,10 +11625,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42871</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="C33" t="n">
@@ -11645,10 +11657,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42962</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42968</v>
       </c>
       <c r="C34" t="n">
@@ -11677,10 +11689,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43053</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="C35" t="n">
@@ -11709,10 +11721,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43167</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43173</v>
       </c>
       <c r="C36" t="n">
@@ -11741,10 +11753,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43243</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43249</v>
       </c>
       <c r="C37" t="n">
@@ -11773,10 +11785,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43334</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43339</v>
       </c>
       <c r="C38" t="n">
@@ -11805,10 +11817,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43425</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43431</v>
       </c>
       <c r="C39" t="n">
@@ -11837,10 +11849,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43531</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="C40" t="n">
@@ -11869,10 +11881,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43609</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="C41" t="n">
@@ -11901,10 +11913,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43703</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="C42" t="n">
@@ -11933,10 +11945,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43791</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="C43" t="n">
@@ -11965,10 +11977,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43895</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43901</v>
       </c>
       <c r="C44" t="n">
@@ -11997,10 +12009,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43973</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="C45" t="n">
@@ -12029,10 +12041,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44064</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="C46" t="n">
@@ -12061,10 +12073,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44155</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="C47" t="n">
@@ -12093,10 +12105,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44259</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="C48" t="n">
@@ -12125,10 +12137,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44337</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="C49" t="n">
@@ -12157,10 +12169,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44428</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="C50" t="n">
@@ -12189,10 +12201,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44519</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="C51" t="n">
@@ -12221,10 +12233,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44623</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44629</v>
       </c>
       <c r="C52" t="n">
@@ -12253,10 +12265,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44701</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="C53" t="n">
@@ -12285,10 +12297,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44792</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="C54" t="n">
@@ -12317,10 +12329,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44883</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44888</v>
       </c>
       <c r="C55" t="n">
@@ -12349,10 +12361,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44987</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="C56" t="n">
@@ -12381,10 +12393,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45065</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C57" t="n">
@@ -12413,10 +12425,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="C58" t="n">
@@ -12445,10 +12457,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45247</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45252</v>
       </c>
       <c r="C59" t="n">
@@ -12477,10 +12489,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45357</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="C60" t="n">
@@ -12509,10 +12521,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45436</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="C61" t="n">
@@ -12541,10 +12553,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="C62" t="n">
@@ -12573,10 +12585,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45617</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="C63" t="n">
@@ -12605,10 +12617,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45721</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="C64" t="n">
@@ -12637,10 +12649,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45800</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="C65" t="n">
@@ -12669,10 +12681,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="C66" t="n">
@@ -12701,10 +12713,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45980</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="C67" t="n">
@@ -12733,10 +12745,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="C68" t="n">
@@ -12765,10 +12777,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="C69" t="n">
@@ -12797,10 +12809,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46262</v>
       </c>
       <c r="C70" t="n">
@@ -12847,12 +12859,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/TGT.xlsx
+++ b/salidas/empresas/TGT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>32.70330047607422</v>
+        <v>32.70329284667969</v>
       </c>
       <c r="C2" t="n">
         <v>54.75</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>32.55297470092773</v>
+        <v>32.55298233032227</v>
       </c>
       <c r="C3" t="n">
         <v>54.40000152587891</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.12278938293457</v>
+        <v>31.12277984619141</v>
       </c>
       <c r="C4" t="n">
         <v>52.0099983215332</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>31.77504539489746</v>
+        <v>31.77502822875977</v>
       </c>
       <c r="C5" t="n">
         <v>53.09999847412109</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.33319091796875</v>
+        <v>29.33320236206055</v>
       </c>
       <c r="C6" t="n">
         <v>48.91999816894531</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>29.30321311950684</v>
+        <v>29.3032112121582</v>
       </c>
       <c r="C7" t="n">
         <v>48.86999893188477</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>27.53435516357422</v>
+        <v>27.53436088562012</v>
       </c>
       <c r="C8" t="n">
         <v>45.91999816894531</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>29.08711051940918</v>
+        <v>29.08708572387695</v>
       </c>
       <c r="C9" t="n">
         <v>48.38999938964844</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>33.21061706542969</v>
+        <v>33.21063232421875</v>
       </c>
       <c r="C10" t="n">
         <v>55.25</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>34.98979568481445</v>
+        <v>34.98979949951172</v>
       </c>
       <c r="C12" t="n">
         <v>58.09000015258789</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>36.95944595336914</v>
+        <v>36.95944976806641</v>
       </c>
       <c r="C14" t="n">
         <v>61.36000061035156</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>37.13320159912109</v>
+        <v>37.13320922851562</v>
       </c>
       <c r="C15" t="n">
         <v>61.52999877929688</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>35.82966613769531</v>
+        <v>35.82964706420898</v>
       </c>
       <c r="C17" t="n">
         <v>59.36999893188477</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>37.75508117675781</v>
+        <v>37.75508880615234</v>
       </c>
       <c r="C18" t="n">
         <v>62.43000030517578</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>38.4626579284668</v>
+        <v>38.46266174316406</v>
       </c>
       <c r="C19" t="n">
         <v>63.59999847412109</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>36.63022613525391</v>
+        <v>36.63022994995117</v>
       </c>
       <c r="C20" t="n">
         <v>60.56999969482422</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>39.96801376342773</v>
+        <v>39.96803665161133</v>
       </c>
       <c r="C21" t="n">
         <v>65.93000030517578</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>38.53734970092773</v>
+        <v>38.5373420715332</v>
       </c>
       <c r="C22" t="n">
         <v>63.56999969482422</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>37.19760894775391</v>
+        <v>37.19760513305664</v>
       </c>
       <c r="C23" t="n">
         <v>61.36000061035156</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>36.44774627685547</v>
+        <v>36.44775772094727</v>
       </c>
       <c r="C24" t="n">
         <v>59.97000122070312</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>30.3883056640625</v>
+        <v>30.3883171081543</v>
       </c>
       <c r="C25" t="n">
         <v>50</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>33.68239974975586</v>
+        <v>33.68241119384766</v>
       </c>
       <c r="C26" t="n">
         <v>55.41999816894531</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>32.05904388427734</v>
+        <v>32.05904006958008</v>
       </c>
       <c r="C27" t="n">
         <v>52.61000061035156</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.88296699523926</v>
+        <v>30.88294982910156</v>
       </c>
       <c r="C28" t="n">
         <v>50.68000030517578</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>32.37590789794922</v>
+        <v>32.37591552734375</v>
       </c>
       <c r="C29" t="n">
         <v>53.13000106811523</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>32.5988883972168</v>
+        <v>32.59888458251953</v>
       </c>
       <c r="C30" t="n">
         <v>53.36000061035156</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.40185928344727</v>
+        <v>28.4018383026123</v>
       </c>
       <c r="C31" t="n">
         <v>46.4900016784668</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.63208961486816</v>
+        <v>27.63207626342773</v>
       </c>
       <c r="C32" t="n">
         <v>45.22999954223633</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>32.49232482910156</v>
+        <v>32.49233245849609</v>
       </c>
       <c r="C33" t="n">
         <v>53.02000045776367</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>30.05937576293945</v>
+        <v>30.05939865112305</v>
       </c>
       <c r="C34" t="n">
         <v>49.04999923706055</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>24.58678817749023</v>
+        <v>24.58680152893066</v>
       </c>
       <c r="C35" t="n">
         <v>40.11999893188477</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.7942008972168</v>
+        <v>20.79421043395996</v>
       </c>
       <c r="C36" t="n">
         <v>33.7599983215332</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.26849365234375</v>
+        <v>21.26848220825195</v>
       </c>
       <c r="C37" t="n">
         <v>34.52999877929688</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.21740341186523</v>
+        <v>19.2174015045166</v>
       </c>
       <c r="C38" t="n">
         <v>31.20000076293945</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>17.53199577331543</v>
+        <v>17.53200149536133</v>
       </c>
       <c r="C39" t="n">
         <v>28.30999946594238</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>21.2972583770752</v>
+        <v>21.29726219177246</v>
       </c>
       <c r="C40" t="n">
         <v>34.38999938964844</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>25.55175590515137</v>
+        <v>25.55174827575684</v>
       </c>
       <c r="C41" t="n">
         <v>41.2599983215332</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>24.43479919433594</v>
+        <v>24.4348030090332</v>
       </c>
       <c r="C42" t="n">
         <v>39.29999923706055</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.54050445556641</v>
+        <v>24.54048919677734</v>
       </c>
       <c r="C43" t="n">
         <v>39.47000122070312</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>27.12076568603516</v>
+        <v>27.12075996398926</v>
       </c>
       <c r="C44" t="n">
         <v>43.61999893188477</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>29.34283065795898</v>
+        <v>29.34284019470215</v>
       </c>
       <c r="C45" t="n">
         <v>47</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>29.14304733276367</v>
+        <v>29.14304542541504</v>
       </c>
       <c r="C46" t="n">
         <v>46.68000030517578</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>30.235595703125</v>
+        <v>30.2356071472168</v>
       </c>
       <c r="C47" t="n">
         <v>48.43000030517578</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.1698055267334</v>
+        <v>29.16980361938477</v>
       </c>
       <c r="C48" t="n">
         <v>46.56000137329102</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>30.30376243591309</v>
+        <v>30.30377960205078</v>
       </c>
       <c r="C49" t="n">
         <v>48.36999893188477</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>32.12060546875</v>
+        <v>32.1206169128418</v>
       </c>
       <c r="C50" t="n">
         <v>51.27000045776367</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>32.38717651367188</v>
+        <v>32.38716125488281</v>
       </c>
       <c r="C51" t="n">
         <v>51.52000045776367</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>33.06609344482422</v>
+        <v>33.06608581542969</v>
       </c>
       <c r="C52" t="n">
         <v>52.59999847412109</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>35.75035095214844</v>
+        <v>35.75034332275391</v>
       </c>
       <c r="C53" t="n">
         <v>56.86999893188477</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>34.38362884521484</v>
+        <v>34.38363265991211</v>
       </c>
       <c r="C54" t="n">
         <v>54.52999877929688</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.00389671325684</v>
+        <v>31.00392150878906</v>
       </c>
       <c r="C55" t="n">
         <v>49.16999816894531</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.35958099365234</v>
+        <v>32.35957717895508</v>
       </c>
       <c r="C56" t="n">
         <v>51.31999969482422</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>32.41781616210938</v>
+        <v>32.41782760620117</v>
       </c>
       <c r="C57" t="n">
         <v>51.15999984741211</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>33.86255645751953</v>
+        <v>33.86256790161133</v>
       </c>
       <c r="C58" t="n">
         <v>53.43999862670898</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>32.91208267211914</v>
+        <v>32.91206741333008</v>
       </c>
       <c r="C59" t="n">
         <v>51.93999862670898</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>36.24882507324219</v>
+        <v>36.24882125854492</v>
       </c>
       <c r="C60" t="n">
         <v>56.93999862670898</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>38.27963256835938</v>
+        <v>38.27964401245117</v>
       </c>
       <c r="C61" t="n">
         <v>60.13000106811523</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.90557098388672</v>
+        <v>34.90558624267578</v>
       </c>
       <c r="C62" t="n">
         <v>54.83000183105469</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>33.60855102539062</v>
+        <v>33.60855865478516</v>
       </c>
       <c r="C63" t="n">
         <v>52.54999923706055</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>31.4020938873291</v>
+        <v>31.4021167755127</v>
       </c>
       <c r="C65" t="n">
         <v>49.09999847412109</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>31.83158874511719</v>
+        <v>31.83157539367676</v>
       </c>
       <c r="C66" t="n">
         <v>49.52999877929688</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.14778709411621</v>
+        <v>30.14777565002441</v>
       </c>
       <c r="C67" t="n">
         <v>46.90999984741211</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>33.09121322631836</v>
+        <v>33.09122085571289</v>
       </c>
       <c r="C68" t="n">
         <v>51.4900016784668</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>33.41390609741211</v>
+        <v>33.41392135620117</v>
       </c>
       <c r="C69" t="n">
         <v>51.66999816894531</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.71315383911133</v>
+        <v>31.71316146850586</v>
       </c>
       <c r="C70" t="n">
         <v>49.04000091552734</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>35.40570068359375</v>
+        <v>35.40569686889648</v>
       </c>
       <c r="C71" t="n">
         <v>54.75</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>34.27373886108398</v>
+        <v>34.27374267578125</v>
       </c>
       <c r="C72" t="n">
         <v>52.70000076293945</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.31122589111328</v>
+        <v>33.31122207641602</v>
       </c>
       <c r="C73" t="n">
         <v>51.22000122070312</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>33.04457473754883</v>
+        <v>33.04457092285156</v>
       </c>
       <c r="C74" t="n">
         <v>50.81000137329102</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>37.08083343505859</v>
+        <v>37.08084487915039</v>
       </c>
       <c r="C75" t="n">
         <v>56.68999862670898</v>
@@ -2138,7 +2138,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>38.11433029174805</v>
+        <v>38.11431884765625</v>
       </c>
       <c r="C76" t="n">
         <v>58.27000045776367</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>38.08496475219727</v>
+        <v>38.08498001098633</v>
       </c>
       <c r="C78" t="n">
         <v>57.90999984741211</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.26910781860352</v>
+        <v>38.26911544799805</v>
       </c>
       <c r="C79" t="n">
         <v>58.18999862670898</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>39.88693618774414</v>
+        <v>39.8869514465332</v>
       </c>
       <c r="C80" t="n">
         <v>60.65000152587891</v>
@@ -2312,7 +2312,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>41.9820442199707</v>
+        <v>41.9820556640625</v>
       </c>
       <c r="C82" t="n">
         <v>63.47000122070312</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>41.99907684326172</v>
+        <v>41.99908065795898</v>
       </c>
       <c r="C84" t="n">
         <v>63.13000106811523</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>39.36456298828125</v>
+        <v>39.36455917358398</v>
       </c>
       <c r="C85" t="n">
         <v>59.16999816894531</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.18950653076172</v>
+        <v>40.18952560424805</v>
       </c>
       <c r="C86" t="n">
         <v>60.40999984741211</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>42.12635803222656</v>
+        <v>42.12636184692383</v>
       </c>
       <c r="C87" t="n">
         <v>62.95999908447266</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>45.79970169067383</v>
+        <v>45.79969787597656</v>
       </c>
       <c r="C88" t="n">
         <v>68.44999694824219</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>47.21149826049805</v>
+        <v>47.21149063110352</v>
       </c>
       <c r="C89" t="n">
         <v>70.55999755859375</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>46.7435417175293</v>
+        <v>46.74355697631836</v>
       </c>
       <c r="C90" t="n">
         <v>69.5</v>
@@ -2573,7 +2573,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>46.3130989074707</v>
+        <v>46.31311416625977</v>
       </c>
       <c r="C91" t="n">
         <v>68.86000061035156</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>47.9205322265625</v>
+        <v>47.92054748535156</v>
       </c>
       <c r="C92" t="n">
         <v>71.25</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.8490104675293</v>
+        <v>42.84900283813477</v>
       </c>
       <c r="C93" t="n">
         <v>63.31000137329102</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.30248641967773</v>
+        <v>43.30246353149414</v>
       </c>
       <c r="C94" t="n">
         <v>63.97999954223633</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>43.85070037841797</v>
+        <v>43.85068130493164</v>
       </c>
       <c r="C95" t="n">
         <v>64.79000091552734</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>43.54859161376953</v>
+        <v>43.54858779907227</v>
       </c>
       <c r="C96" t="n">
         <v>63.93000030517578</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>43.0989875793457</v>
+        <v>43.09899139404297</v>
       </c>
       <c r="C97" t="n">
         <v>63.27000045776367</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>38.58270645141602</v>
+        <v>38.58269119262695</v>
       </c>
       <c r="C98" t="n">
         <v>56.63999938964844</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>42.92635345458984</v>
+        <v>42.92636489868164</v>
       </c>
       <c r="C99" t="n">
         <v>62.54000091552734</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>41.53298950195312</v>
+        <v>41.53299713134766</v>
       </c>
       <c r="C100" t="n">
         <v>60.5099983215332</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>42.38412475585938</v>
+        <v>42.38411331176758</v>
       </c>
       <c r="C101" t="n">
         <v>61.75</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>39.24686050415039</v>
+        <v>39.24686813354492</v>
       </c>
       <c r="C102" t="n">
         <v>56.7599983215332</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>40.06968307495117</v>
+        <v>40.06968688964844</v>
       </c>
       <c r="C103" t="n">
         <v>57.95000076293945</v>
@@ -2950,7 +2950,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>41.20366287231445</v>
+        <v>41.20367050170898</v>
       </c>
       <c r="C104" t="n">
         <v>59.59000015258789</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>41.91001892089844</v>
+        <v>41.9100227355957</v>
       </c>
       <c r="C105" t="n">
         <v>60.06999969482422</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>43.73097991943359</v>
+        <v>43.73097610473633</v>
       </c>
       <c r="C106" t="n">
         <v>62.68000030517578</v>
@@ -3037,7 +3037,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>43.13096618652344</v>
+        <v>43.13097763061523</v>
       </c>
       <c r="C107" t="n">
         <v>61.81999969482422</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.02587127685547</v>
+        <v>52.02587509155273</v>
       </c>
       <c r="C108" t="n">
         <v>74</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>53.36872100830078</v>
+        <v>53.36870956420898</v>
       </c>
       <c r="C109" t="n">
         <v>75.91000366210938</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>51.75169372558594</v>
+        <v>51.75168991088867</v>
       </c>
       <c r="C110" t="n">
         <v>73.61000061035156</v>
@@ -3209,7 +3209,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>55.7990837097168</v>
+        <v>55.79907989501953</v>
       </c>
       <c r="C113" t="n">
         <v>78.83000183105469</v>
@@ -3236,7 +3236,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>56.52017593383789</v>
+        <v>56.52016448974609</v>
       </c>
       <c r="C114" t="n">
         <v>79.31999969482422</v>
@@ -3263,7 +3263,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>58.16618728637695</v>
+        <v>58.16621780395508</v>
       </c>
       <c r="C115" t="n">
         <v>81.62999725341797</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>58.32296371459961</v>
+        <v>58.32293319702148</v>
       </c>
       <c r="C116" t="n">
         <v>81.84999847412109</v>
@@ -3317,7 +3317,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>55.76652526855469</v>
+        <v>55.76653289794922</v>
       </c>
       <c r="C117" t="n">
         <v>77.70999908447266</v>
@@ -3344,7 +3344,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>56.44826889038086</v>
+        <v>56.44825744628906</v>
       </c>
       <c r="C118" t="n">
         <v>78.66000366210938</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>55.38619995117188</v>
+        <v>55.38618087768555</v>
       </c>
       <c r="C119" t="n">
         <v>77.18000030517578</v>
@@ -3398,7 +3398,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>52.43616104125977</v>
+        <v>52.4361686706543</v>
       </c>
       <c r="C120" t="n">
         <v>72.5</v>
@@ -3425,7 +3425,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>52.51572799682617</v>
+        <v>52.51573944091797</v>
       </c>
       <c r="C121" t="n">
         <v>72.61000061035156</v>
@@ -3452,7 +3452,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>52.37830352783203</v>
+        <v>52.3783073425293</v>
       </c>
       <c r="C122" t="n">
         <v>72.41999816894531</v>
@@ -3479,7 +3479,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>57.21035766601562</v>
+        <v>57.21035003662109</v>
       </c>
       <c r="C123" t="n">
         <v>78.44999694824219</v>
@@ -3506,7 +3506,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.0034065246582</v>
+        <v>60.00339508056641</v>
       </c>
       <c r="C124" t="n">
         <v>82.27999877929688</v>
@@ -3535,7 +3535,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>57.97607803344727</v>
+        <v>57.97607421875</v>
       </c>
       <c r="C125" t="n">
         <v>79.5</v>
@@ -3564,7 +3564,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>50.54150772094727</v>
+        <v>50.54150390625</v>
       </c>
       <c r="C126" t="n">
         <v>68.77999877929688</v>
@@ -3593,7 +3593,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>51.30572891235352</v>
+        <v>51.30573272705078</v>
       </c>
       <c r="C127" t="n">
         <v>69.81999969482422</v>
@@ -3622,7 +3622,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>55.35466003417969</v>
+        <v>55.35464859008789</v>
       </c>
       <c r="C128" t="n">
         <v>75.33000183105469</v>
@@ -3680,7 +3680,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>50.87065505981445</v>
+        <v>50.87065887451172</v>
       </c>
       <c r="C130" t="n">
         <v>68.68000030517578</v>
@@ -3709,7 +3709,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>50.90767669677734</v>
+        <v>50.90768814086914</v>
       </c>
       <c r="C131" t="n">
         <v>68.73000335693359</v>
@@ -3738,7 +3738,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.69614028930664</v>
+        <v>57.69616317749023</v>
       </c>
       <c r="C132" t="n">
         <v>77.23999786376953</v>
@@ -3767,7 +3767,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>53.95380401611328</v>
+        <v>53.95382690429688</v>
       </c>
       <c r="C133" t="n">
         <v>72.23000335693359</v>
@@ -3796,7 +3796,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>48.16477966308594</v>
+        <v>48.16476821899414</v>
       </c>
       <c r="C134" t="n">
         <v>64.48000335693359</v>
@@ -3825,7 +3825,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.30398941040039</v>
+        <v>44.30399322509766</v>
       </c>
       <c r="C135" t="n">
         <v>58.77000045776367</v>
@@ -3883,7 +3883,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>42.10273361206055</v>
+        <v>42.10272979736328</v>
       </c>
       <c r="C137" t="n">
         <v>55.84999847412109</v>
@@ -3912,7 +3912,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>42.02694702148438</v>
+        <v>42.02693939208984</v>
       </c>
       <c r="C138" t="n">
         <v>55.15000152587891</v>
@@ -3941,7 +3941,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>39.84749221801758</v>
+        <v>39.84748840332031</v>
       </c>
       <c r="C139" t="n">
         <v>52.29000091552734</v>
@@ -3970,7 +3970,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>43.18524932861328</v>
+        <v>43.18525314331055</v>
       </c>
       <c r="C140" t="n">
         <v>56.66999816894531</v>
@@ -3999,7 +3999,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>42.02264022827148</v>
+        <v>42.02264785766602</v>
       </c>
       <c r="C141" t="n">
         <v>54.52999877929688</v>
@@ -4028,7 +4028,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>45.47508239746094</v>
+        <v>45.47509002685547</v>
       </c>
       <c r="C142" t="n">
         <v>59.0099983215332</v>
@@ -4086,7 +4086,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>46.63969421386719</v>
+        <v>46.63970184326172</v>
       </c>
       <c r="C144" t="n">
         <v>59.90000152587891</v>
@@ -4115,7 +4115,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>50.80535125732422</v>
+        <v>50.80535888671875</v>
       </c>
       <c r="C145" t="n">
         <v>65.25</v>
@@ -4144,7 +4144,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>58.56824493408203</v>
+        <v>58.56826400756836</v>
       </c>
       <c r="C146" t="n">
         <v>75.22000122070312</v>
@@ -4173,7 +4173,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>59.20107650756836</v>
+        <v>59.20105361938477</v>
       </c>
       <c r="C147" t="n">
         <v>75.41000366210938</v>
@@ -4202,7 +4202,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>54.50642776489258</v>
+        <v>54.50643539428711</v>
       </c>
       <c r="C148" t="n">
         <v>69.43000030517578</v>
@@ -4231,7 +4231,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>56.99505615234375</v>
+        <v>56.99507904052734</v>
       </c>
       <c r="C149" t="n">
         <v>72.59999847412109</v>
@@ -4260,7 +4260,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>57.71358489990234</v>
+        <v>57.71355819702148</v>
       </c>
       <c r="C150" t="n">
         <v>72.88999938964844</v>
@@ -4289,7 +4289,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>60.27103042602539</v>
+        <v>60.27105331420898</v>
       </c>
       <c r="C151" t="n">
         <v>76.12000274658203</v>
@@ -4318,7 +4318,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>63.88159561157227</v>
+        <v>63.88160705566406</v>
       </c>
       <c r="C152" t="n">
         <v>80.68000030517578</v>
@@ -4405,7 +4405,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>66.73786163330078</v>
+        <v>66.73786926269531</v>
       </c>
       <c r="C155" t="n">
         <v>83.62999725341797</v>
@@ -4463,7 +4463,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>53.17823028564453</v>
+        <v>53.1782341003418</v>
       </c>
       <c r="C157" t="n">
         <v>66.08999633789062</v>
@@ -4492,7 +4492,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>58.73825454711914</v>
+        <v>58.73824691772461</v>
       </c>
       <c r="C158" t="n">
         <v>73</v>
@@ -4521,7 +4521,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>58.9666862487793</v>
+        <v>58.96669387817383</v>
       </c>
       <c r="C159" t="n">
         <v>72.63999938964844</v>
@@ -4550,7 +4550,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>65.15232849121094</v>
+        <v>65.15236663818359</v>
       </c>
       <c r="C160" t="n">
         <v>80.26000213623047</v>
@@ -4579,7 +4579,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>62.84692764282227</v>
+        <v>62.84693908691406</v>
       </c>
       <c r="C161" t="n">
         <v>77.41999816894531</v>
@@ -4608,7 +4608,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>65.89493560791016</v>
+        <v>65.89492797851562</v>
       </c>
       <c r="C162" t="n">
         <v>80.44999694824219</v>
@@ -4637,7 +4637,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>70.94044494628906</v>
+        <v>70.94047546386719</v>
       </c>
       <c r="C163" t="n">
         <v>86.61000061035156</v>
@@ -4666,7 +4666,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>70.76846313476562</v>
+        <v>70.76844787597656</v>
       </c>
       <c r="C164" t="n">
         <v>86.40000152587891</v>
@@ -4695,7 +4695,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>88.34771728515625</v>
+        <v>88.34772491455078</v>
       </c>
       <c r="C165" t="n">
         <v>107.0400009155273</v>
@@ -4724,7 +4724,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>88.24044036865234</v>
+        <v>88.24044799804688</v>
       </c>
       <c r="C166" t="n">
         <v>106.9100036621094</v>
@@ -4753,7 +4753,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>88.24044036865234</v>
+        <v>88.24044799804688</v>
       </c>
       <c r="C167" t="n">
         <v>106.9100036621094</v>
@@ -4782,7 +4782,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>103.79150390625</v>
+        <v>103.7914962768555</v>
       </c>
       <c r="C168" t="n">
         <v>125.0100021362305</v>
@@ -4811,7 +4811,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>106.448356628418</v>
+        <v>106.4483642578125</v>
       </c>
       <c r="C169" t="n">
         <v>128.2100067138672</v>
@@ -4840,7 +4840,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>91.94361114501953</v>
+        <v>91.943603515625</v>
       </c>
       <c r="C170" t="n">
         <v>110.7399978637695</v>
@@ -4869,7 +4869,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>86.0040283203125</v>
+        <v>86.00404357910156</v>
       </c>
       <c r="C171" t="n">
         <v>103</v>
@@ -4898,7 +4898,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>77.62906646728516</v>
+        <v>77.62908172607422</v>
       </c>
       <c r="C172" t="n">
         <v>92.97000122070312</v>
@@ -4927,7 +4927,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>91.63188934326172</v>
+        <v>91.63186645507812</v>
       </c>
       <c r="C173" t="n">
         <v>109.7399978637695</v>
@@ -4956,7 +4956,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>102.6857299804688</v>
+        <v>102.6857070922852</v>
       </c>
       <c r="C174" t="n">
         <v>122.3300018310547</v>
@@ -4985,7 +4985,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>100.6711120605469</v>
+        <v>100.6711273193359</v>
       </c>
       <c r="C175" t="n">
         <v>119.9300003051758</v>
@@ -5014,7 +5014,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>105.6656265258789</v>
+        <v>105.6656646728516</v>
       </c>
       <c r="C176" t="n">
         <v>125.879997253418</v>
@@ -5043,7 +5043,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>127.5554733276367</v>
+        <v>127.5554809570312</v>
       </c>
       <c r="C177" t="n">
         <v>151.2100067138672</v>
@@ -5072,7 +5072,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>132.7940216064453</v>
+        <v>132.7939910888672</v>
       </c>
       <c r="C178" t="n">
         <v>157.4199981689453</v>
@@ -5130,7 +5130,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>152.0713043212891</v>
+        <v>152.0712890625</v>
       </c>
       <c r="C180" t="n">
         <v>179.5299987792969</v>
@@ -5159,7 +5159,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>149.5301513671875</v>
+        <v>149.5301361083984</v>
       </c>
       <c r="C181" t="n">
         <v>176.5299987792969</v>
@@ -5188,7 +5188,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>153.4604644775391</v>
+        <v>153.46044921875</v>
       </c>
       <c r="C182" t="n">
         <v>181.1699981689453</v>
@@ -5217,7 +5217,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>155.9371795654297</v>
+        <v>155.9371948242188</v>
       </c>
       <c r="C183" t="n">
         <v>183.4400024414062</v>
@@ -5246,7 +5246,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>168.3737182617188</v>
+        <v>168.3737335205078</v>
       </c>
       <c r="C184" t="n">
         <v>198.0700073242188</v>
@@ -5275,7 +5275,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>176.1858978271484</v>
+        <v>176.1858825683594</v>
       </c>
       <c r="C185" t="n">
         <v>207.2599945068359</v>
@@ -5304,7 +5304,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>193.5249176025391</v>
+        <v>193.52490234375</v>
       </c>
       <c r="C186" t="n">
         <v>226.9199981689453</v>
@@ -5333,7 +5333,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>206.1638946533203</v>
+        <v>206.1638793945312</v>
       </c>
       <c r="C187" t="n">
         <v>241.7400054931641</v>
@@ -5362,7 +5362,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>222.6320648193359</v>
+        <v>222.6321411132812</v>
       </c>
       <c r="C188" t="n">
         <v>261.0499877929688</v>
@@ -5420,7 +5420,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>195.772216796875</v>
+        <v>195.7722015380859</v>
       </c>
       <c r="C190" t="n">
         <v>228.7700042724609</v>
@@ -5449,7 +5449,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>222.1723785400391</v>
+        <v>222.1723937988281</v>
       </c>
       <c r="C191" t="n">
         <v>259.6199951171875</v>
@@ -5507,7 +5507,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>198.7337341308594</v>
+        <v>198.7337493896484</v>
       </c>
       <c r="C193" t="n">
         <v>231.4400024414062</v>
@@ -5536,7 +5536,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>189.2796325683594</v>
+        <v>189.2796478271484</v>
       </c>
       <c r="C194" t="n">
         <v>220.4299926757812</v>
@@ -5565,7 +5565,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>172.2826538085938</v>
+        <v>172.2826385498047</v>
       </c>
       <c r="C195" t="n">
         <v>199.7700042724609</v>
@@ -5652,7 +5652,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>140.1815643310547</v>
+        <v>140.1815795898438</v>
       </c>
       <c r="C198" t="n">
         <v>161.8800048828125</v>
@@ -5681,7 +5681,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>122.2994537353516</v>
+        <v>122.2994918823242</v>
       </c>
       <c r="C199" t="n">
         <v>141.2299957275391</v>
@@ -5710,7 +5710,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>141.4805145263672</v>
+        <v>141.4804840087891</v>
       </c>
       <c r="C200" t="n">
         <v>163.3800048828125</v>
@@ -5739,7 +5739,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>139.7182464599609</v>
+        <v>139.7182159423828</v>
       </c>
       <c r="C201" t="n">
         <v>160.3399963378906</v>
@@ -5768,7 +5768,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>129.3052062988281</v>
+        <v>129.3051910400391</v>
       </c>
       <c r="C202" t="n">
         <v>148.3899993896484</v>
@@ -5797,7 +5797,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>143.1253814697266</v>
+        <v>143.1253967285156</v>
       </c>
       <c r="C203" t="n">
         <v>164.25</v>
@@ -5826,7 +5826,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>146.495849609375</v>
+        <v>146.4958648681641</v>
       </c>
       <c r="C204" t="n">
         <v>167.0700073242188</v>
@@ -5855,7 +5855,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>130.6861877441406</v>
+        <v>130.6861724853516</v>
       </c>
       <c r="C205" t="n">
         <v>149.0399932861328</v>
@@ -5884,7 +5884,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>150.9414825439453</v>
+        <v>150.9414978027344</v>
       </c>
       <c r="C206" t="n">
         <v>172.1399993896484</v>
@@ -5913,7 +5913,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>148.6761932373047</v>
+        <v>148.6761779785156</v>
       </c>
       <c r="C207" t="n">
         <v>168.5</v>
@@ -5942,7 +5942,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>146.1438598632812</v>
+        <v>146.1438446044922</v>
       </c>
       <c r="C208" t="n">
         <v>165.6300048828125</v>
@@ -5971,7 +5971,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>139.1908874511719</v>
+        <v>139.1909027099609</v>
       </c>
       <c r="C209" t="n">
         <v>157.75</v>
@@ -6029,7 +6029,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>117.1702194213867</v>
+        <v>117.1702117919922</v>
       </c>
       <c r="C211" t="n">
         <v>131.8999938964844</v>
@@ -6058,7 +6058,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>121.2298812866211</v>
+        <v>121.2298889160156</v>
       </c>
       <c r="C212" t="n">
         <v>136.4700012207031</v>
@@ -6087,7 +6087,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>113.3813629150391</v>
+        <v>113.38134765625</v>
       </c>
       <c r="C213" t="n">
         <v>126.5500030517578</v>
@@ -6116,7 +6116,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>99.06421661376953</v>
+        <v>99.06422424316406</v>
       </c>
       <c r="C214" t="n">
         <v>110.5699996948242</v>
@@ -6145,7 +6145,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>99.26131439208984</v>
+        <v>99.26132965087891</v>
       </c>
       <c r="C215" t="n">
         <v>110.7900009155273</v>
@@ -6174,7 +6174,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>121.1276550292969</v>
+        <v>121.1276321411133</v>
       </c>
       <c r="C216" t="n">
         <v>133.8099975585938</v>
@@ -6261,7 +6261,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>139.4517517089844</v>
+        <v>139.4517364501953</v>
       </c>
       <c r="C219" t="n">
         <v>152.9199981689453</v>
@@ -6319,7 +6319,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>146.8018646240234</v>
+        <v>146.8018493652344</v>
       </c>
       <c r="C221" t="n">
         <v>160.9799957275391</v>
@@ -6348,7 +6348,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>143.3866577148438</v>
+        <v>143.3866119384766</v>
       </c>
       <c r="C222" t="n">
         <v>156.1600036621094</v>
@@ -6377,7 +6377,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>135.9308471679688</v>
+        <v>135.9308166503906</v>
       </c>
       <c r="C223" t="n">
         <v>148.0399932861328</v>
@@ -6406,7 +6406,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>138.1069641113281</v>
+        <v>138.1069793701172</v>
       </c>
       <c r="C224" t="n">
         <v>150.4100036621094</v>
@@ -6435,7 +6435,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>142.1575317382812</v>
+        <v>142.1575469970703</v>
       </c>
       <c r="C225" t="n">
         <v>153.6199951171875</v>
@@ -6464,7 +6464,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>144.2304077148438</v>
+        <v>144.2304229736328</v>
       </c>
       <c r="C226" t="n">
         <v>155.8600006103516</v>
@@ -6522,7 +6522,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>123.322998046875</v>
+        <v>123.3229904174805</v>
       </c>
       <c r="C228" t="n">
         <v>132.3099975585938</v>
@@ -6551,7 +6551,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>125.9980392456055</v>
+        <v>125.9980545043945</v>
       </c>
       <c r="C229" t="n">
         <v>135.1799926757812</v>
@@ -6580,7 +6580,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>128.5426330566406</v>
+        <v>128.5426177978516</v>
       </c>
       <c r="C230" t="n">
         <v>137.9100036621094</v>
@@ -6609,7 +6609,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>116.7887115478516</v>
+        <v>116.788703918457</v>
       </c>
       <c r="C231" t="n">
         <v>124.2399978637695</v>
@@ -6667,7 +6667,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>90.90042114257812</v>
+        <v>90.90041351318359</v>
       </c>
       <c r="C233" t="n">
         <v>96.69999694824219</v>
@@ -6725,7 +6725,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>93.79361724853516</v>
+        <v>93.79360198974609</v>
       </c>
       <c r="C235" t="n">
         <v>98.65000152587891</v>
@@ -6754,7 +6754,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>95.55253601074219</v>
+        <v>95.55252838134766</v>
       </c>
       <c r="C236" t="n">
         <v>100.5</v>
@@ -6812,7 +6812,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>86.20908355712891</v>
+        <v>86.20909118652344</v>
       </c>
       <c r="C238" t="n">
         <v>89.69999694824219</v>
@@ -6841,7 +6841,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>89.11155700683594</v>
+        <v>89.11156463623047</v>
       </c>
       <c r="C239" t="n">
         <v>92.72000122070312</v>
@@ -6870,7 +6870,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>88.19110870361328</v>
+        <v>88.19110107421875</v>
       </c>
       <c r="C240" t="n">
         <v>90.62000274658203</v>
@@ -6928,7 +6928,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>102.6430740356445</v>
+        <v>102.64306640625</v>
       </c>
       <c r="C242" t="n">
         <v>105.4700012207031</v>
